--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_13_Monitoring, Logging _ Observability/Day_13_FULL_TOAN_BO_76_CAU.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_13_Monitoring, Logging _ Observability/Day_13_FULL_TOAN_BO_76_CAU.xlsx
@@ -1167,7 +1167,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1195,7 +1195,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>P=1−(1−0,01)^10=1−0,99^10≈9,56%.</t>
+          <t>Xác suất gặp ít nhất một lượt latency &gt; 5s trong 10 lượt chat độc lập: P = 1 - (1 - 0,01)^10 = 1 - 0,99^10 ≈ 0,0956178... = 9,56%.</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -1352,7 +1352,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn signal thực sự so output với evidence hoặc authority.</t>
+          <t>Đánh giá rủi ro hallucination khi dữ liệu lớn đòi hỏi phối hợp đa tầng: (a) Kiểm tra đối chiếu tự động giữa thực thể/claim với nguồn truy xuất (groundedness check), (b) lấy mẫu định kỳ chấm bằng LLM judge có version cố định, (c) chuyển chuyên gia con người hoặc hệ thống hồ sơ gốc (system-of-record) rà soát các trường hợp bất đồng có rủi ro cao.</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>60</v>
@@ -1400,7 +1400,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Tool success rate, Timeout rate.</t>
+          <t>Báo cáo số liệu công cụ chính xác: Tỷ lệ thành công là 80/100 = 80%; các tỷ lệ lỗi (timeout, invalid schema, provider failure) và tỷ lệ lặp lại (loop rate) phải được tính toán dựa trên đúng mẫu số tương ứng.</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="G24" s="3" t="n"/>
       <c r="H24" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>60</v>
@@ -1722,7 +1722,7 @@
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Correlation, Provider/model/version.</t>
+          <t>Tập trường tối thiểu cần thiết để debug độ trễ và chi phí theo model/prompt mà không làm rò rỉ PII: Mã định danh tương quan, phiên bản prompt/model, số lượng token, thời gian xử lý và kết quả thực thi.</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="G26" s="3" t="n"/>
       <c r="H26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>60</v>
@@ -1830,7 +1830,7 @@
       <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Pre-render redaction, Regex và entity recognition.</t>
+          <t>Nguyên tắc che dữ liệu nhạy cảm (PII redaction): Việc làm sạch dữ liệu phải được thực hiện tại ranh giới ứng dụng trước khi phát đi (redact-before-emission), ngăn chặn PII lọt vào bất kỳ bộ đệm trace hay log nào.</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="G31" s="3" t="n"/>
       <c r="H31" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31" s="4" t="n">
         <v>60</v>
@@ -2089,7 +2089,7 @@
       <c r="J31" s="3" t="n"/>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Execution context, Context binding.</t>
+          <t>Trong các ứng dụng bất đồng bộ chạy nhiều coroutines, dữ liệu ngữ cảnh của người dùng phải được cô lập độc lập theo từng task (sử dụng `contextvars.ContextVar`) để tránh tình trạng race-condition gây lẫn lộn thông tin tenant.</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99100</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -2137,7 +2137,7 @@
       <c r="J32" s="3" t="n"/>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách error khỏi normal trước khi áp sampling rate.</t>
+          <t>Tổng số event giữ lại: Error events (100% của 1% * 1.000.000 = 10.000) + Normal events (9% của 99% * 1.000.000 = 0,09 * 990.000 = 89.100). Tổng cộng: 10.000 + 89.100 = 99.100 event.</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="G34" s="3" t="n"/>
       <c r="H34" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I34" s="4" t="n">
         <v>60</v>
@@ -2245,7 +2245,7 @@
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Trace identity, Root/child span.</t>
+          <t>Trong kiến trúc microservices và hàng đợi async, trace context bắt buộc phải được truyền (propagate) và liên kết xuyên suốt qua các message queue để bảo đảm quan hệ nhân quả (causality) giữa các span.</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="G35" s="3" t="n"/>
       <c r="H35" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I35" s="4" t="n">
         <v>60</v>
@@ -2293,7 +2293,7 @@
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Root invocation, Model generation span.</t>
+          <t>Thiết kế span hữu ích cho agent loop: Nên phân tách span theo từng tác vụ thao tác cụ thể (plan, retrieve, model call, tool execution, retry) thay vì gom toàn bộ vào một span duy nhất hoặc chia vụn theo từng token.</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I38" s="4" t="n">
@@ -2451,7 +2451,7 @@
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn các rule dùng outcome nhưng không mở rộng data risk.</t>
+          <t>Chính sách tail-sampling hiệu quả khi lưu lượng lớn và buffer hữu hạn: (a) Giữ lại 100% các vết có lỗi, độ trễ cao hoặc chi phí bất thường, (b) lấy mẫu lưu lượng bình thường theo ngân sách cố định, (c) đặt giới hạn buffer để chống tràn bộ nhớ và ghi nhận rõ tỷ lệ lấy mẫu.</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G39" s="3" t="n"/>
       <c r="H39" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>60</v>
@@ -2499,7 +2499,7 @@
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Sequential dependency, External waiting.</t>
+          <t>Biểu đồ waterfall cho thấy tool A và tool B chạy tuần tự mất 2s + 2s dù hoàn toàn độc lập; mẫu hình tắc nghẽn là thực thi nối tiếp (serial execution) và giải pháp tối ưu là chạy song song hai công cụ.</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="G40" s="3" t="n"/>
       <c r="H40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>60</v>
@@ -2547,7 +2547,7 @@
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Prompt name/label/version, Resolved source.</t>
+          <t>Nhãn 'production' là tham chiếu động; để bảo đảm khả năng kiểm toán và phục hồi chính xác, hệ thống telemetry bắt buộc phải ghi lại mã băm (hash) hoặc số phiên bản cụ thể của prompt đã được phân giải.</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="G42" s="3" t="n"/>
       <c r="H42" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I42" s="4" t="n">
         <v>60</v>
@@ -2643,7 +2643,7 @@
       <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Collector, Metric route.</t>
+          <t>Để loại bỏ tình trạng duplicate dữ liệu trace khi gửi trực tiếp và qua collector, kiến trúc chuẩn là định tuyến toàn bộ telemetry qua một OpenTelemetry Collector duy nhất và cấu hình fan-out rõ ràng tại đó.</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="G44" s="3" t="n"/>
       <c r="H44" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" s="4" t="n">
         <v>60</v>
@@ -2749,7 +2749,7 @@
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Request counter, Latency observation.</t>
+          <t>Ghi nhận chỉ số đo lường chính xác: Tăng bộ đếm request ngay khi tiếp nhận (ingress), đo thời gian xử lý trong khối `finally`, và chỉ gắn nhãn thành công/thất bại tại sự kiện kết thúc cuối cùng.</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50000000000000</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -2797,7 +2797,7 @@
       <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Nhân số giá trị độc lập của từng label.</t>
+          <t>Upper bound số time series: Tích số các giá trị cardinality của từng metric label = 1.000.000 (user_id) * 10.000.000 (request_id) * 5 (model) = 5 * 10^13 = 50.000.000.000.000 series.</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="G47" s="3" t="n"/>
       <c r="H47" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I47" s="4" t="n">
         <v>60</v>
@@ -2893,7 +2893,7 @@
       <c r="J47" s="3" t="n"/>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Overview, Engineering detail.</t>
+          <t>Thiết kế bảng điều khiển trực quan hiệu quả theo nguyên lý phân cấp nhận thức: Bắt đầu từ màn hình tổng quan mức cao (Overview) → xem chi tiết kỹ thuật (Detail) → cho phép đi sâu vào từng vết sự cố (Drill-down).</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="G48" s="3" t="n"/>
       <c r="H48" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I48" s="4" t="n">
         <v>60</v>
@@ -2941,7 +2941,7 @@
       <c r="J48" s="3" t="n"/>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Named panel profile, Traffic.</t>
+          <t>Bảng điều khiển hiện tại vi phạm nghiêm trọng yêu cầu đặc tả vì thiếu cả bốn liên kết chỉ số trọng yếu: TTFT P95, chi phí tác vụ P95, tỷ lệ lỗi công cụ và độ tin cậy nội dung (groundedness).</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G51" s="3" t="n"/>
       <c r="H51" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I51" s="4" t="n">
         <v>60</v>
@@ -3097,7 +3097,7 @@
       <c r="J51" s="3" t="n"/>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Versioned definition, Code review.</t>
+          <t>Để bảo đảm tính nhất quán và khả năng tái lập giữa các môi trường, toàn bộ cấu hình bảng điều khiển phải được quản lý dưới dạng mã nguồn (Dashboard-as-Code), có quy trình kiểm thử và review trước khi triển khai.</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="G52" s="3" t="n"/>
       <c r="H52" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I52" s="4" t="n">
         <v>60</v>
@@ -3145,7 +3145,7 @@
       <c r="J52" s="3" t="n"/>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: User-visible symptom, Cause candidate.</t>
+          <t>Nguyên tắc phát cảnh báo SRE: Chỉ phát cảnh báo khẩn cấp (page on-call) khi có triệu chứng ảnh hưởng trực tiếp đến người dùng (breach SLO/latency); các chỉ số tài nguyên như GPU 95% chỉ dùng để chẩn đoán nguyên nhân.</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="G53" s="3" t="n"/>
       <c r="H53" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" s="4" t="n">
         <v>60</v>
@@ -3193,7 +3193,7 @@
       <c r="J53" s="3" t="n"/>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Condition/duration, Severity.</t>
+          <t>Cảnh báo có thể hành động được (actionable alert) bắt buộc phải cung cấp đầy đủ: Điều kiện kích hoạt, thời gian duy trì, mức độ ảnh hưởng, liên kết bằng chứng và quy trình/người chịu trách nhiệm xử lý.</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -3395,7 +3395,7 @@
       <c r="J57" s="3" t="n"/>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đổi 0,1% thành tỷ lệ rồi nhân tổng phút trong window.</t>
+          <t>Tổng số phút trong cửa sổ 30 ngày: 30 ngày * 24 giờ/ngày * 60 phút/giờ = 43.200 phút. Thời gian downtime cho phép với SLO 99,9%: 43.200 * (100% - 99,9%) = 43.200 * 0,001 = 43,2 phút.</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="G59" s="3" t="n"/>
       <c r="H59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>60</v>
@@ -3491,7 +3491,7 @@
       <c r="J59" s="3" t="n"/>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Burn-rate denominator, Short window.</t>
+          <t>Quy tắc cảnh báo đa cửa sổ (multi-window multi-burn-rate) yêu cầu cả cửa sổ ngắn (5m) và cửa sổ dài (1h) đều phải vượt ngưỡng; hiện tại cửa sổ dài mới đạt 8x (&lt; 14,4x) nên không được phát trang khẩn cấp để tránh báo động giả.</t>
         </is>
       </c>
     </row>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -3635,7 +3635,7 @@
       <c r="J62" s="3" t="n"/>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Loại record duplicate trước khi sum.</t>
+          <t>Sau khi deduplicate record trùng call_id với call 0,003 USD, chi phí task chỉ tính các unique calls: 0,002 + 0,005 + 0,003 = 0,01 USD.</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="G64" s="3" t="n"/>
       <c r="H64" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I64" s="4" t="n">
         <v>60</v>
@@ -3731,7 +3731,7 @@
       <c r="J64" s="3" t="n"/>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: User, Feature.</t>
+          <t>Để phân bổ chi phí và trả lời câu hỏi của CFO về mức tiêu hao ngân sách theo từng khách hàng, bản ghi telemetry bắt buộc phải gắn thẻ định danh khách hàng (`tenant_id`).</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I65" s="4" t="n">
@@ -3786,7 +3786,7 @@
       <c r="J65" s="3" t="n"/>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách population cố định trước release khỏi traffic thật sau release.</t>
+          <t>Phân biệt rạch ròi giữa offline eval và online eval: (a) Fixed benchmark trước release -&gt; offline eval; (b) Sample traffic thật sau release -&gt; online eval; (c) CI regression gate -&gt; offline eval; (d) Production drift/cohort monitoring -&gt; online eval.</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -3930,7 +3930,7 @@
       <c r="J68" s="3" t="n"/>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính sample volume trước rồi nhân unit cost.</t>
+          <t>Chi phí eval hàng ngày: 1.000.000 requests * 1% sample rate * 0,002 USD/sampled request = 10.000 requests * 0,002 USD = 20 USD/ngày.</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="G69" s="3" t="n"/>
       <c r="H69" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I69" s="4" t="n">
         <v>60</v>
@@ -3978,7 +3978,7 @@
       <c r="J69" s="3" t="n"/>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Quality failure candidate, Feedback hoặc judge evidence.</t>
+          <t>Khi một trường hợp lỗi ở production có chứa dữ liệu nhạy cảm PII, quy trình đưa vào tập kiểm thử offline bắt buộc là phải làm sạch (sanitize/redact) dữ liệu PII và được chuyên gia thẩm định trước khi lưu trữ.</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="G70" s="3" t="n"/>
       <c r="H70" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I70" s="4" t="n">
         <v>60</v>
@@ -4026,7 +4026,7 @@
       <c r="J70" s="3" t="n"/>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Judge identity/version, Score distribution.</t>
+          <t>Khi điểm số của LLM judge sụt giảm sau khi nâng cấp phiên bản nhưng độ đồng thuận của judge với nhãn chuyên gia cũng giảm, bước đầu tiên là phải kiểm tra sự lệch lạc của chính bộ đánh giá (evaluator drift).</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="G73" s="3" t="n"/>
       <c r="H73" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I73" s="4" t="n">
         <v>60</v>
@@ -4170,7 +4170,7 @@
       <c r="J73" s="3" t="n"/>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Personal-data flow, Processor/vendor.</t>
+          <t>Khi dữ liệu cá nhân của người dùng Việt Nam được chuyển ra máy chủ nước ngoài mà chưa rõ điều khoản xử lý dữ liệu và căn cứ pháp lý, hành động đúng là gắn cờ cảnh báo để đội ngũ pháp lý rà soát tuân thủ.</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="G76" s="3" t="n"/>
       <c r="H76" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I76" s="4" t="n">
         <v>60</v>
@@ -4321,7 +4321,7 @@
       <c r="J76" s="3" t="n"/>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Span anomaly, Baseline comparison.</t>
+          <t>Dữ liệu trace cho thấy bước retrieval chậm nhưng chưa có thông tin về triển khai thay đổi hay kiểm chứng khắc phục; quan sát này mới chỉ cấu thành một giả thuyết nguyên nhân (cause candidate) chứ chưa phải kết luận gốc rễ.</t>
         </is>
       </c>
     </row>
